--- a/output/pdf_financials_xlsx/PEC.H.xlsx
+++ b/output/pdf_financials_xlsx/PEC.H.xlsx
@@ -5778,7 +5778,7 @@
         <v>1.986</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2.84</v>
+        <v>5.68</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>4.773</v>
@@ -5836,7 +5836,7 @@
         <v>5.909</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>5.937</v>
+        <v>11.874</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>6.028</v>

--- a/output/pdf_financials_xlsx/PEC.H.xlsx
+++ b/output/pdf_financials_xlsx/PEC.H.xlsx
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.046</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.437</v>
+        <v>6.773</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-134.868</v>
+        <v>-135.222</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-7.197</v>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.437</v>
+        <v>6.773</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-134.868</v>
+        <v>-135.222</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-7.197</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.710730948678071</v>
+        <v>7.022291342664593</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-313.9897096826764</v>
+        <v>-314.8138663189998</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-23.42011064106736</v>
@@ -2372,55 +2372,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>11.896</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.655</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>5.517</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.518</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.978</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.08805399999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001329</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000786</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.001721</v>
       </c>
     </row>
     <row r="35">
@@ -2488,55 +2488,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.021</v>
+        <v>14.917</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.789</v>
+        <v>3.609</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.362</v>
+        <v>4.182</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.909</v>
+        <v>1.919</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.409</v>
+        <v>5.064</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>5.526</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.509</v>
+        <v>11.556</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.509</v>
+        <v>11.556</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4.509</v>
+        <v>5.027</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.983</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.606</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.176</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.271</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.08805399999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001329</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000786</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.001721</v>
       </c>
     </row>
     <row r="37">
@@ -3184,46 +3184,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>103.65</v>
+        <v>91.754</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>24.753</v>
+        <v>21.933</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.547</v>
+        <v>0.727</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.708</v>
+        <v>3.698</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>19.659</v>
+        <v>15.004</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>10.796</v>
+        <v>5.279</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>12.838</v>
+        <v>3.791</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>12.838</v>
+        <v>3.791</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.7</v>
+        <v>1.182</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>9.843999999999999</v>
+        <v>8.866</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.33</v>
+        <v>4.729</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.7</v>
+        <v>2.529</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.743</v>
+        <v>4.477</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.095717</v>
+        <v>0.007663</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -32392,7 +32392,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -35690,7 +35690,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -88179,7 +88179,7 @@
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E800" s="5" t="n">
@@ -88280,7 +88280,7 @@
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E801" s="5" t="n">
